--- a/stories/arbres/TREE-COL-023.xlsx
+++ b/stories/arbres/TREE-COL-023.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Lina est avec papa, sous le pommier. Lina a envie de jouer. papa est là, tout près. On va apprendre : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina écoute papa. Lina entend les mots : bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lina va vers la cuisine. Un vélo passe au loin. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Lina se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On range un objet. papa dit : je suis là. On reste ensemble.</t>
+          <t>Lina va vers la cuisine. Un vélo passe au loin. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Lina se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On range un objet. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers la cuisine. Un vélo passe au loin. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Lina se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On range un objet.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : dire le mot. Lina respire. Lina retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi les cubes. Il y a des miettes sur la table. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2584,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2751,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le matin. La couverture est douce. On range un objet. Cette fin-là est celle de la cuisine, les cubes et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2918,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3085,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint après la sieste. On entend un oiseau. On dit merci. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3252,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3419,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le soir. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3586,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3753,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le livre. Un chat miaule une fois. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3944,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4111,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le matin. On entend un oiseau. On range un objet. Cette fin-là est celle de la cuisine, le livre et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4278,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4445,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint après la sieste. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de la cuisine, le livre et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4612,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4779,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le soir. Le vent est doux. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4946,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5113,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi la dînette. Les chaussures font toc toc. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5304,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5471,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le matin. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de la cuisine, la dînette et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5638,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5805,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint après la sieste. Le vent est doux. On dit merci. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5972,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6139,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le soir. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6306,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6167,7 +6335,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Lina va vers le jardin. La lumière est claire. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Lina se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On dit merci. papa dit : je suis là. On reste ensemble.</t>
+          <t>Lina va vers le jardin. La lumière est claire. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Lina se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6305,6 +6473,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers le jardin. La lumière est claire. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Lina se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On dit merci.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6659,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6832,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : dire le mot. Lina respire. Lina retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6839,6 +7023,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7001,6 +7190,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi les cubes. La couverture est douce. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7381,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7349,6 +7548,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le matin. On entend un oiseau. On dit merci. Cette fin-là est celle de le jardin, les cubes et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7715,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7882,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint après la sieste. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8049,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8216,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le soir. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8383,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8550,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le livre. On entend un oiseau. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8741,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8908,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le matin. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le jardin, le livre et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9075,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9242,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint après la sieste. Le vent est doux. On souffle doucement. Cette fin-là est celle de le jardin, le livre et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9409,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9317,6 +9576,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le soir. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9743,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9910,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi la dînette. Ça sent le pain chaud. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10101,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9989,6 +10268,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le matin. Le vent est doux. On dit merci. Cette fin-là est celle de le jardin, la dînette et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10435,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10313,6 +10602,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint après la sieste. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10769,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10637,6 +10936,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le soir. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11103,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10823,7 +11132,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Lina va vers la chambre. Il y a des miettes sur la table. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Lina se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On souffle doucement. papa dit : je suis là. On reste ensemble.</t>
+          <t>Lina va vers la chambre. Il y a des miettes sur la table. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Lina se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10961,6 +11270,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers la chambre. Il y a des miettes sur la table. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Lina se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On souffle doucement.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11141,6 +11456,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
     </row>
@@ -11309,6 +11629,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : dire le mot. Lina respire. Lina retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11495,6 +11820,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11657,6 +11987,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi les cubes. Le vent est doux. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12178,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12345,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le matin. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12512,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12329,6 +12679,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint après la sieste. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12846,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13013,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le soir. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la chambre, les cubes et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13180,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12977,6 +13347,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le livre. Le sol est un peu froid. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13538,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13325,6 +13705,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le matin. Le vent est doux. On souffle doucement. Cette fin-là est celle de la chambre, le livre et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13872,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13649,6 +14039,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint après la sieste. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14206,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13973,6 +14373,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le soir. Une feuille tombe. On attend son tour. Cette fin-là est celle de la chambre, le livre et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14540,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14297,6 +14707,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi la dînette. Une feuille tombe. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14898,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15065,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le matin. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15232,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15399,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint après la sieste. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15566,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15293,6 +15733,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint le soir. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la chambre, la dînette et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15900,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15490,6 +15940,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-023.xlsx
+++ b/stories/arbres/TREE-COL-023.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Lina est avec papa, sous le pommier. Lina a envie de jouer. papa est là, tout près. On va apprendre : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina écoute papa. Lina entend les mots : bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : dire le mot. Lina respire. Lina retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Lina a choisi les cubes. Il y a des miettes sur la table. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2589,6 +2601,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2756,6 +2769,7 @@
           <t>narrateur|Lina rejoint le matin. La couverture est douce. On range un objet. Cette fin-là est celle de la cuisine, les cubes et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2923,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3090,6 +3105,7 @@
           <t>narrateur|Lina rejoint après la sieste. On entend un oiseau. On dit merci. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3257,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3424,6 +3441,7 @@
           <t>narrateur|Lina rejoint le soir. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3591,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3758,6 +3777,7 @@
           <t>narrateur|Lina a choisi le livre. Un chat miaule une fois. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3949,6 +3969,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4116,6 +4137,7 @@
           <t>narrateur|Lina rejoint le matin. On entend un oiseau. On range un objet. Cette fin-là est celle de la cuisine, le livre et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4283,6 +4305,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4450,6 +4473,7 @@
           <t>narrateur|Lina rejoint après la sieste. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de la cuisine, le livre et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4617,6 +4641,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4784,6 +4809,7 @@
           <t>narrateur|Lina rejoint le soir. Le vent est doux. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4951,6 +4977,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5118,6 +5145,7 @@
           <t>narrateur|Lina a choisi la dînette. Les chaussures font toc toc. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5309,6 +5337,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5476,6 +5505,7 @@
           <t>narrateur|Lina rejoint le matin. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de la cuisine, la dînette et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5643,6 +5673,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5810,6 +5841,7 @@
           <t>narrateur|Lina rejoint après la sieste. Le vent est doux. On dit merci. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5977,6 +6009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6144,6 +6177,7 @@
           <t>narrateur|Lina rejoint le soir. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6311,6 +6345,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6479,6 +6514,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6666,6 +6702,7 @@
           <t>narrateur|Que fait-on ? Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6837,6 +6874,7 @@
           <t>narrateur|Oui. Voici le geste : dire le mot. Lina respire. Lina retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7028,6 +7066,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7195,6 +7234,7 @@
           <t>narrateur|Lina a choisi les cubes. La couverture est douce. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7386,6 +7426,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7553,6 +7594,7 @@
           <t>narrateur|Lina rejoint le matin. On entend un oiseau. On dit merci. Cette fin-là est celle de le jardin, les cubes et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7720,6 +7762,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7887,6 +7930,7 @@
           <t>narrateur|Lina rejoint après la sieste. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8054,6 +8098,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8221,6 +8266,7 @@
           <t>narrateur|Lina rejoint le soir. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8388,6 +8434,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8555,6 +8602,7 @@
           <t>narrateur|Lina a choisi le livre. On entend un oiseau. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8746,6 +8794,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8913,6 +8962,7 @@
           <t>narrateur|Lina rejoint le matin. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le jardin, le livre et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9080,6 +9130,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9247,6 +9298,7 @@
           <t>narrateur|Lina rejoint après la sieste. Le vent est doux. On souffle doucement. Cette fin-là est celle de le jardin, le livre et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9414,6 +9466,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9581,6 +9634,7 @@
           <t>narrateur|Lina rejoint le soir. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9748,6 +9802,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9915,6 +9970,7 @@
           <t>narrateur|Lina a choisi la dînette. Ça sent le pain chaud. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10106,6 +10162,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10273,6 +10330,7 @@
           <t>narrateur|Lina rejoint le matin. Le vent est doux. On dit merci. Cette fin-là est celle de le jardin, la dînette et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10440,6 +10498,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10607,6 +10666,7 @@
           <t>narrateur|Lina rejoint après la sieste. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10774,6 +10834,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10941,6 +11002,7 @@
           <t>narrateur|Lina rejoint le soir. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11108,6 +11170,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11276,6 +11339,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11463,6 +11527,7 @@
           <t>narrateur|Que fait-on ? Bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11634,6 +11699,7 @@
           <t>narrateur|Oui. Voici le geste : dire le mot. Lina respire. Lina retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11825,6 +11891,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11992,6 +12059,7 @@
           <t>narrateur|Lina a choisi les cubes. Le vent est doux. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12183,6 +12251,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12350,6 +12419,7 @@
           <t>narrateur|Lina rejoint le matin. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12517,6 +12587,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12684,6 +12755,7 @@
           <t>narrateur|Lina rejoint après la sieste. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12851,6 +12923,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13018,6 +13091,7 @@
           <t>narrateur|Lina rejoint le soir. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la chambre, les cubes et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13185,6 +13259,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13352,6 +13427,7 @@
           <t>narrateur|Lina a choisi le livre. Le sol est un peu froid. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13543,6 +13619,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13710,6 +13787,7 @@
           <t>narrateur|Lina rejoint le matin. Le vent est doux. On souffle doucement. Cette fin-là est celle de la chambre, le livre et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13877,6 +13955,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14044,6 +14123,7 @@
           <t>narrateur|Lina rejoint après la sieste. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14211,6 +14291,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14378,6 +14459,7 @@
           <t>narrateur|Lina rejoint le soir. Une feuille tombe. On attend son tour. Cette fin-là est celle de la chambre, le livre et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14545,6 +14627,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14712,6 +14795,7 @@
           <t>narrateur|Lina a choisi la dînette. Une feuille tombe. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14903,6 +14987,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15070,6 +15155,7 @@
           <t>narrateur|Lina rejoint le matin. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15237,6 +15323,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15404,6 +15491,7 @@
           <t>narrateur|Lina rejoint après la sieste. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15571,6 +15659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15738,6 +15827,7 @@
           <t>narrateur|Lina rejoint le soir. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la chambre, la dînette et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15905,6 +15995,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15923,7 +16014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15947,6 +16038,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15961,7 +16066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16148,6 +16253,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-COL-023.xlsx
+++ b/stories/arbres/TREE-COL-023.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bonjour, s'il te plaît, merci — sous le pommier</t>
+          <t>Le banc mouillé et la pomme de Mila</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sous le pommier, le banc est encore mouillé. Mila veut une pomme, un panier, un jeu. Elle dit bonjour, s'il te plaît, merci, avec papa et maman.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Lina est avec papa, sous le pommier. Lina a envie de jouer. papa est là, tout près. On va apprendre : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina écoute papa. Lina entend les mots : bonjour, s'il te plaît, merci.</t>
+          <t>Le banc de bois reste mouillé, sous le pommier. Une goutte glisse sur le dossier. Elle fait ploc dans l'herbe. Une pomme jaune a une tache brune. Une feuille colle à la chaussette de Mila. La porte de la maison est ouverte. Ça sent la soupe, tout doux. Un panier a un trou, tout petit. Papa essuie une pomme sur sa manche. Maman pose un torchon sur la branche. Tu sens, Mila ? Ça sent la pomme. Elle est froide. Le banc est encore mouillé. En ce moment, Mila touche le bois. Le bois est rêche, puis lisse. Bonjour, pommier. Bonjour, Mila. On dit les mots, ici aussi. Bonjour. S'il te plaît. Merci. Une abeille passe, tout loin, tout bas. Le torchon bouge un peu, sur la branche.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,10 +1337,37 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Lina est avec papa, sous le pommier. Lina a envie de jouer. papa est là, tout près. On va apprendre : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina écoute papa. Lina entend les mots : bonjour, s'il te plaît, merci.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le banc de bois reste mouillé, sous le pommier.
+narrateur|Une goutte glisse sur le dossier.
+narrateur|Elle fait ploc dans l'herbe.
+narrateur|Une pomme jaune a une tache brune.
+narrateur|Une feuille colle à la chaussette de Mila.
+narrateur|La porte de la maison est ouverte.
+narrateur|Ça sent la soupe, tout doux.
+narrateur|Un panier a un trou, tout petit.
+narrateur|Papa essuie une pomme sur sa manche.
+narrateur|Maman pose un torchon sur la branche.
+papa|Tu sens, Mila ?
+papa|Ça sent la pomme.
+enfant-f|Elle est froide.
+maman|Le banc est encore mouillé.
+narrateur|En ce moment, Mila touche le bois.
+narrateur|Le bois est rêche, puis lisse.
+enfant-f|Bonjour, pommier.
+papa|Bonjour, Mila.
+maman|On dit les mots, ici aussi.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+narrateur|Une abeille passe, tout loin, tout bas.
+narrateur|Le torchon bouge un peu, sur la branche.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>goutte,oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1353,7 +1392,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>Trois coins de la maison attendent. La cuisine, le jardin, ou la chambre ? On dit bonjour. On dit merci.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1517,7 +1556,10 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>narrateur|Trois coins de la maison attendent.
+papa|La cuisine, le jardin, ou la chambre ?
+maman|On dit bonjour.
+maman|On dit merci.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1545,7 +1587,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lina va vers la cuisine. Un vélo passe au loin. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Lina se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On range un objet. Je suis là. On reste ensemble.</t>
+          <t>Mila pousse la porte de la cuisine. Le carrelage est un peu froid. Une pomme jaune attend dans le saladier. Ça sent le sucre et le bois. Papa essuie encore sa manche. Bonjour, papa. Bonjour, Mila. Tu veux la pomme jaune ? Oui. S'il te plaît. Papa pose la pomme dans sa main. La peau est lisse, un peu froide. Merci, papa. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Une goutte de jus brille sur la table.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,11 +1727,32 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Lina va vers la cuisine. Un vélo passe au loin. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Lina se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On range un objet.
-papa|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Mila pousse la porte de la cuisine.
+narrateur|Le carrelage est un peu froid.
+narrateur|Une pomme jaune attend dans le saladier.
+narrateur|Ça sent le sucre et le bois.
+narrateur|Papa essuie encore sa manche.
+enfant-f|Bonjour, papa.
+papa|Bonjour, Mila.
+papa|Tu veux la pomme jaune ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+narrateur|Papa pose la pomme dans sa main.
+narrateur|La peau est lisse, un peu froide.
+enfant-f|Merci, papa.
+maman|Bravo, Mila.
+maman|Tu as dit les mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+narrateur|Une goutte de jus brille sur la table.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>assiette</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1714,7 +1777,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Bonjour, s'il te plaît, merci.</t>
+          <t>Papa arrive, dans la cuisine. Mila dit quoi ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1874,7 +1937,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Bonjour, s'il te plaît, merci.</t>
+          <t>narrateur|Papa arrive, dans la cuisine.
+maman|Mila dit quoi ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1902,7 +1966,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : dire le mot. Lina respire. Lina retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
+          <t>Oui. On dit bonjour. On dit s'il te plaît. On dit merci. Mila souffle un peu. La pomme jaune reste froide dans sa main. Bonjour. Merci. Bravo, Mila. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2046,7 +2110,16 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : dire le mot. Lina respire. Lina retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
+          <t>papa|Oui.
+papa|On dit bonjour.
+papa|On dit s'il te plaît.
+papa|On dit merci.
+narrateur|Mila souffle un peu.
+narrateur|La pomme jaune reste froide dans sa main.
+enfant-f|Bonjour.
+enfant-f|Merci.
+maman|Bravo, Mila.
+maman|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2074,7 +2147,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Trois jeux attendent, tout proches. Les cubes, le livre, ou la dînette ? On demande. On dit merci.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2238,7 +2311,10 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Trois jeux attendent, tout proches.
+maman|Les cubes, le livre, ou la dînette ?
+papa|On demande.
+papa|On dit merci.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2266,7 +2342,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Lina a choisi les cubes. Il y a des miettes sur la table. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
+          <t>Mila prend les cubes en bois. Un cube rouge sent le pin. Un cube vert fait clic. Tu veux le cube rouge ? S'il te plaît. Papa tend le cube, tout lentement. Merci, papa. Bravo. Tu as demandé. Puis tu as dit merci. On dit s'il te plaît. On dit merci. Mila pose le cube, tout droit. Un cube attrape un reflet de pomme. On est encore dans la cuisine. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2406,10 +2482,30 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Lina a choisi les cubes. Il y a des miettes sur la table. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Mila prend les cubes en bois.
+narrateur|Un cube rouge sent le pin.
+narrateur|Un cube vert fait clic.
+papa|Tu veux le cube rouge ?
+enfant-f|S'il te plaît.
+narrateur|Papa tend le cube, tout lentement.
+enfant-f|Merci, papa.
+maman|Bravo.
+maman|Tu as demandé.
+maman|Puis tu as dit merci.
+papa|On dit s'il te plaît.
+papa|On dit merci.
+narrateur|Mila pose le cube, tout droit.
+narrateur|Un cube attrape un reflet de pomme.
+narrateur|On est encore dans la cuisine.
+maman|On dit s'il te plaît.
+maman|On dit merci.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>cubes</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2434,7 +2530,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On dit encore les mots.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2598,7 +2694,9 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On dit encore les mots.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2626,7 +2724,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint le matin. La couverture est douce. On range un objet. Cette fin-là est celle de la cuisine, les cubes et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. La rosée brille encore, tout loin. Ça sent le cacao, un peu. Bonjour, Mila. Bonjour, papa. Mila a encore les cubes, dans la cuisine. Un cube jaune attrape le soleil sur la table. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2766,10 +2864,33 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint le matin. La couverture est douce. On range un objet. Cette fin-là est celle de la cuisine, les cubes et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|La rosée brille encore, tout loin.
+narrateur|Ça sent le cacao, un peu.
+papa|Bonjour, Mila.
+enfant-f|Bonjour, papa.
+narrateur|Mila a encore les cubes, dans la cuisine.
+narrateur|Un cube jaune attrape le soleil sur la table.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range les cubes, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2794,7 +2915,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu le matin, dans la cuisine. Elle a joué avec les cubes. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2934,7 +3055,15 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu le matin, dans la cuisine.
+narrateur|Elle a joué avec les cubes.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2962,7 +3091,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint après la sieste. On entend un oiseau. On dit merci. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Tu es réveillée ? Oui, maman. Mila a encore les cubes, dans la cuisine. Un cube fait un clic, tout petit, près du bol. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3102,7 +3231,26 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint après la sieste. On entend un oiseau. On dit merci. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+narrateur|Mila a encore les cubes, dans la cuisine.
+narrateur|Un cube fait un clic, tout petit, près du bol.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3130,7 +3278,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu après la sieste, dans la cuisine. Elle a joué avec les cubes. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3270,7 +3418,15 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu après la sieste, dans la cuisine.
+narrateur|Elle a joué avec les cubes.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3298,7 +3454,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint le soir. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Te voilà, Mila. Bonjour, papa. Mila a encore les cubes, dans la cuisine. La lampe allonge l'ombre des cubes. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3438,10 +3594,33 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint le soir. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+papa|Te voilà, Mila.
+enfant-f|Bonjour, papa.
+narrateur|Mila a encore les cubes, dans la cuisine.
+narrateur|La lampe allonge l'ombre des cubes.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range les cubes, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3466,7 +3645,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu le soir, dans la cuisine. Elle a joué avec les cubes. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3606,7 +3785,15 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu le soir, dans la cuisine.
+narrateur|Elle a joué avec les cubes.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3634,7 +3821,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Lina a choisi le livre. Un chat miaule une fois. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
+          <t>Mila ouvre le livre. La page sent le papier, un peu sec. Une pomme est dessinée, toute rouge. On lit ensemble ? Oui. S'il te plaît. Maman tourne la page, tout doux. Merci, maman. Bravo, Mila. Tu as dit s'il te plaît. Et merci, maintenant. Merci. Mila caresse la pomme du livre. Une goutte de jus reste au bord de la page. On est encore dans la cuisine. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3774,10 +3961,30 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Lina a choisi le livre. Un chat miaule une fois. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Mila ouvre le livre.
+narrateur|La page sent le papier, un peu sec.
+narrateur|Une pomme est dessinée, toute rouge.
+maman|On lit ensemble ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+narrateur|Maman tourne la page, tout doux.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit s'il te plaît.
+maman|Et merci, maintenant.
+enfant-f|Merci.
+narrateur|Mila caresse la pomme du livre.
+narrateur|Une goutte de jus reste au bord de la page.
+narrateur|On est encore dans la cuisine.
+maman|On dit s'il te plaît.
+maman|On dit merci.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3802,7 +4009,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On dit encore les mots.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3966,7 +4173,9 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On dit encore les mots.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3994,7 +4203,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint le matin. On entend un oiseau. On range un objet. Cette fin-là est celle de la cuisine, le livre et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. La rosée brille encore, tout loin. Ça sent le cacao, un peu. Bonjour, Mila. Bonjour, papa. Mila a encore le livre, dans la cuisine. Une miette reste collée sur la page. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4134,10 +4343,33 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint le matin. On entend un oiseau. On range un objet. Cette fin-là est celle de la cuisine, le livre et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|La rosée brille encore, tout loin.
+narrateur|Ça sent le cacao, un peu.
+papa|Bonjour, Mila.
+enfant-f|Bonjour, papa.
+narrateur|Mila a encore le livre, dans la cuisine.
+narrateur|Une miette reste collée sur la page.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range le livre, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4162,7 +4394,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu le matin, dans la cuisine. Elle a joué avec le livre. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4302,7 +4534,15 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu le matin, dans la cuisine.
+narrateur|Elle a joué avec le livre.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4330,7 +4570,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint après la sieste. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de la cuisine, le livre et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Tu es réveillée ? Oui, maman. Mila a encore le livre, dans la cuisine. Le livre est un peu chaud, comme la nappe. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4470,7 +4710,26 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint après la sieste. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de la cuisine, le livre et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+narrateur|Mila a encore le livre, dans la cuisine.
+narrateur|Le livre est un peu chaud, comme la nappe.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range le livre, tout doux.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4498,7 +4757,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu après la sieste, dans la cuisine. Elle a joué avec le livre. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4638,7 +4897,15 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu après la sieste, dans la cuisine.
+narrateur|Elle a joué avec le livre.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4666,7 +4933,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint le soir. Le vent est doux. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Te voilà, Mila. Bonjour, papa. Mila a encore le livre, dans la cuisine. La pomme du livre brille sous la lampe. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4806,10 +5073,33 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint le soir. Le vent est doux. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+papa|Te voilà, Mila.
+enfant-f|Bonjour, papa.
+narrateur|Mila a encore le livre, dans la cuisine.
+narrateur|La pomme du livre brille sous la lampe.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range le livre, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4834,7 +5124,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu le soir, dans la cuisine. Elle a joué avec le livre. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4974,7 +5264,15 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu le soir, dans la cuisine.
+narrateur|Elle a joué avec le livre.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5002,7 +5300,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Lina a choisi la dînette. Les chaussures font toc toc. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On montre du doigt, sans courir. maman n'est pas loin.</t>
+          <t>Mila prend la dînette. Une petite assiette sonne, tout creux. Une cuillère miniature est encore tiède. Tu sers la soupe ? S'il te plaît, la casserole. Oui. Tiens. Merci. Bravo. Tu as dit les mots. Bonjour, petite casserole. Bonjour. Mila pose l'assiette, tout doux. La petite casserole est près du saladier. On est encore dans la cuisine. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5142,10 +5440,30 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Lina a choisi la dînette. Les chaussures font toc toc. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On montre du doigt, sans courir. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|Mila prend la dînette.
+narrateur|Une petite assiette sonne, tout creux.
+narrateur|Une cuillère miniature est encore tiède.
+papa|Tu sers la soupe ?
+enfant-f|S'il te plaît, la casserole.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci.
+papa|Bravo.
+papa|Tu as dit les mots.
+maman|Bonjour, petite casserole.
+enfant-f|Bonjour.
+narrateur|Mila pose l'assiette, tout doux.
+narrateur|La petite casserole est près du saladier.
+narrateur|On est encore dans la cuisine.
+maman|On dit s'il te plaît.
+maman|On dit merci.</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>assiette</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5170,7 +5488,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On dit encore les mots.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5334,7 +5652,9 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On dit encore les mots.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5362,7 +5682,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint le matin. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de la cuisine, la dînette et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. La rosée brille encore, tout loin. Ça sent le cacao, un peu. Bonjour, Mila. Bonjour, papa. Mila a encore la dînette, dans la cuisine. La petite casserole sent encore la pomme. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5502,10 +5822,33 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint le matin. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de la cuisine, la dînette et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|La rosée brille encore, tout loin.
+narrateur|Ça sent le cacao, un peu.
+papa|Bonjour, Mila.
+enfant-f|Bonjour, papa.
+narrateur|Mila a encore la dînette, dans la cuisine.
+narrateur|La petite casserole sent encore la pomme.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range la dînette, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5530,7 +5873,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu le matin, dans la cuisine. Elle a joué avec la dînette. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5670,7 +6013,15 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu le matin, dans la cuisine.
+narrateur|Elle a joué avec la dînette.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5698,7 +6049,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint après la sieste. Le vent est doux. On dit merci. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Tu es réveillée ? Oui, maman. Mila a encore la dînette, dans la cuisine. Une cuillère miniature tremble près du bol. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5838,7 +6189,26 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint après la sieste. Le vent est doux. On dit merci. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+narrateur|Mila a encore la dînette, dans la cuisine.
+narrateur|Une cuillère miniature tremble près du bol.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5866,7 +6236,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu après la sieste, dans la cuisine. Elle a joué avec la dînette. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6006,7 +6376,15 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu après la sieste, dans la cuisine.
+narrateur|Elle a joué avec la dînette.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6034,7 +6412,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint le soir. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Te voilà, Mila. Bonjour, papa. Mila a encore la dînette, dans la cuisine. La dînette fait un tout petit ding. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6174,10 +6552,33 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint le soir. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+papa|Te voilà, Mila.
+enfant-f|Bonjour, papa.
+narrateur|Mila a encore la dînette, dans la cuisine.
+narrateur|La dînette fait un tout petit ding.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range la dînette, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6202,7 +6603,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu le soir, dans la cuisine. Elle a joué avec la dînette. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6342,7 +6743,15 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu le soir, dans la cuisine.
+narrateur|Elle a joué avec la dînette.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6370,7 +6779,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Lina va vers le jardin. La lumière est claire. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Lina se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On dit merci. Je suis là. On reste ensemble.</t>
+          <t>Mila revient sous le pommier. L'herbe colle encore à ses chaussettes. Le banc de bois reste mouillé. Une pomme rouge brille dans l'herbe. Bonjour, maman. Bonjour, ma grande. Tu veux le panier ? Oui. S'il te plaît. Maman tend le panier troué. L'anse est rêche, tout douce ensuite. Merci, maman. Bravo, Mila. Tu as dit merci. On dit bonjour. On dit s'il te plaît. On dit merci. Une feuille tourne, tout lentement.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6510,11 +6919,31 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Lina va vers le jardin. La lumière est claire. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Lina se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On dit merci.
-papa|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Mila revient sous le pommier.
+narrateur|L'herbe colle encore à ses chaussettes.
+narrateur|Le banc de bois reste mouillé.
+narrateur|Une pomme rouge brille dans l'herbe.
+enfant-f|Bonjour, maman.
+maman|Bonjour, ma grande.
+maman|Tu veux le panier ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+narrateur|Maman tend le panier troué.
+narrateur|L'anse est rêche, tout douce ensuite.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit merci.
+maman|On dit bonjour.
+maman|On dit s'il te plaît.
+maman|On dit merci.
+narrateur|Une feuille tourne, tout lentement.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6539,7 +6968,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Bonjour, s'il te plaît, merci.</t>
+          <t>Mila veut le panier. Elle dit quoi ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6699,7 +7128,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Bonjour, s'il te plaît, merci.</t>
+          <t>narrateur|Mila veut le panier.
+papa|Elle dit quoi ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6727,7 +7157,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : dire le mot. Lina respire. Lina retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
+          <t>Oui. On dit s'il te plaît. On dit merci. Mila serre l'anse du panier. S'il te plaît. Merci. Bravo. Tu as dit les mots. Une pomme rouge roule, tout près.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6871,7 +7301,15 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : dire le mot. Lina respire. Lina retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
+          <t>maman|Oui.
+maman|On dit s'il te plaît.
+maman|On dit merci.
+narrateur|Mila serre l'anse du panier.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+papa|Bravo.
+papa|Tu as dit les mots.
+narrateur|Une pomme rouge roule, tout près.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6899,7 +7337,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Trois jeux attendent, tout proches. Les cubes, le livre, ou la dînette ? On demande. On dit merci.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7063,7 +7501,10 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Trois jeux attendent, tout proches.
+maman|Les cubes, le livre, ou la dînette ?
+papa|On demande.
+papa|On dit merci.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7091,7 +7532,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Lina a choisi les cubes. La couverture est douce. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
+          <t>Mila prend les cubes en bois. Un cube rouge sent le pin. Un cube vert fait clic. Tu veux le cube rouge ? S'il te plaît. Papa tend le cube, tout lentement. Merci, papa. Bravo. Tu as demandé. Puis tu as dit merci. On dit s'il te plaît. On dit merci. Mila pose le cube, tout droit. L'herbe tache un cube, tout vert. On est encore dans le jardin. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7231,10 +7672,30 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Lina a choisi les cubes. La couverture est douce. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Mila prend les cubes en bois.
+narrateur|Un cube rouge sent le pin.
+narrateur|Un cube vert fait clic.
+papa|Tu veux le cube rouge ?
+enfant-f|S'il te plaît.
+narrateur|Papa tend le cube, tout lentement.
+enfant-f|Merci, papa.
+maman|Bravo.
+maman|Tu as demandé.
+maman|Puis tu as dit merci.
+papa|On dit s'il te plaît.
+papa|On dit merci.
+narrateur|Mila pose le cube, tout droit.
+narrateur|L'herbe tache un cube, tout vert.
+narrateur|On est encore dans le jardin.
+maman|On dit s'il te plaît.
+maman|On dit merci.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>cubes</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7259,7 +7720,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On dit encore les mots.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7423,7 +7884,9 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On dit encore les mots.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7451,7 +7914,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint le matin. On entend un oiseau. On dit merci. Cette fin-là est celle de le jardin, les cubes et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. La rosée brille encore, tout loin. Ça sent le cacao, un peu. Bonjour, Mila. Bonjour, papa. Mila a encore les cubes, dans le jardin. L'herbe mouille un cube, tout vert. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7591,10 +8054,33 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint le matin. On entend un oiseau. On dit merci. Cette fin-là est celle de le jardin, les cubes et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|La rosée brille encore, tout loin.
+narrateur|Ça sent le cacao, un peu.
+papa|Bonjour, Mila.
+enfant-f|Bonjour, papa.
+narrateur|Mila a encore les cubes, dans le jardin.
+narrateur|L'herbe mouille un cube, tout vert.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range les cubes, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7619,7 +8105,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu le matin, dans le jardin. Elle a joué avec les cubes. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7759,7 +8245,15 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu le matin, dans le jardin.
+narrateur|Elle a joué avec les cubes.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7787,7 +8281,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint après la sieste. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Tu es réveillée ? Oui, maman. Mila a encore les cubes, dans le jardin. Un cube sèche au soleil, près du banc. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7927,7 +8421,26 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint après la sieste. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+narrateur|Mila a encore les cubes, dans le jardin.
+narrateur|Un cube sèche au soleil, près du banc.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7955,7 +8468,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu après la sieste, dans le jardin. Elle a joué avec les cubes. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8095,7 +8608,15 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu après la sieste, dans le jardin.
+narrateur|Elle a joué avec les cubes.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8123,7 +8644,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint le soir. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Te voilà, Mila. Bonjour, papa. Mila a encore les cubes, dans le jardin. Un cube garde une goutte, toute ronde. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8263,10 +8784,33 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint le soir. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+papa|Te voilà, Mila.
+enfant-f|Bonjour, papa.
+narrateur|Mila a encore les cubes, dans le jardin.
+narrateur|Un cube garde une goutte, toute ronde.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range les cubes, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8291,7 +8835,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu le soir, dans le jardin. Elle a joué avec les cubes. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8431,7 +8975,15 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu le soir, dans le jardin.
+narrateur|Elle a joué avec les cubes.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8459,7 +9011,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Lina a choisi le livre. On entend un oiseau. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
+          <t>Mila ouvre le livre. La page sent le papier, un peu sec. Une pomme est dessinée, toute rouge. On lit ensemble ? Oui. S'il te plaît. Maman tourne la page, tout doux. Merci, maman. Bravo, Mila. Tu as dit s'il te plaît. Et merci, maintenant. Merci. Mila caresse la pomme du livre. Une vraie feuille sert de marque-page. On est encore dans le jardin. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8599,10 +9151,30 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Lina a choisi le livre. On entend un oiseau. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Mila ouvre le livre.
+narrateur|La page sent le papier, un peu sec.
+narrateur|Une pomme est dessinée, toute rouge.
+maman|On lit ensemble ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+narrateur|Maman tourne la page, tout doux.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit s'il te plaît.
+maman|Et merci, maintenant.
+enfant-f|Merci.
+narrateur|Mila caresse la pomme du livre.
+narrateur|Une vraie feuille sert de marque-page.
+narrateur|On est encore dans le jardin.
+maman|On dit s'il te plaît.
+maman|On dit merci.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8627,7 +9199,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On dit encore les mots.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8791,7 +9363,9 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On dit encore les mots.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8819,7 +9393,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint le matin. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le jardin, le livre et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. La rosée brille encore, tout loin. Ça sent le cacao, un peu. Bonjour, Mila. Bonjour, papa. Mila a encore le livre, dans le jardin. Une feuille vraie marque encore la page. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8959,10 +9533,33 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint le matin. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le jardin, le livre et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|La rosée brille encore, tout loin.
+narrateur|Ça sent le cacao, un peu.
+papa|Bonjour, Mila.
+enfant-f|Bonjour, papa.
+narrateur|Mila a encore le livre, dans le jardin.
+narrateur|Une feuille vraie marque encore la page.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range le livre, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8987,7 +9584,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu le matin, dans le jardin. Elle a joué avec le livre. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9127,7 +9724,15 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu le matin, dans le jardin.
+narrateur|Elle a joué avec le livre.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9155,7 +9760,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint après la sieste. Le vent est doux. On souffle doucement. Cette fin-là est celle de le jardin, le livre et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Tu es réveillée ? Oui, maman. Mila a encore le livre, dans le jardin. Le livre sent l'herbe, un peu. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9295,7 +9900,26 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint après la sieste. Le vent est doux. On souffle doucement. Cette fin-là est celle de le jardin, le livre et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+narrateur|Mila a encore le livre, dans le jardin.
+narrateur|Le livre sent l'herbe, un peu.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range le livre, tout doux.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9323,7 +9947,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu après la sieste, dans le jardin. Elle a joué avec le livre. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9463,7 +10087,15 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu après la sieste, dans le jardin.
+narrateur|Elle a joué avec le livre.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9491,7 +10123,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint le soir. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Te voilà, Mila. Bonjour, papa. Mila a encore le livre, dans le jardin. Un oiseau chante. Le livre reste ouvert. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9631,10 +10263,34 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint le soir. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+papa|Te voilà, Mila.
+enfant-f|Bonjour, papa.
+narrateur|Mila a encore le livre, dans le jardin.
+narrateur|Un oiseau chante.
+narrateur|Le livre reste ouvert.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range le livre, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9659,7 +10315,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu le soir, dans le jardin. Elle a joué avec le livre. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9799,7 +10455,15 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu le soir, dans le jardin.
+narrateur|Elle a joué avec le livre.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9827,7 +10491,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Lina a choisi la dînette. Ça sent le pain chaud. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On montre du doigt, sans courir. maman n'est pas loin.</t>
+          <t>Mila prend la dînette. Une petite assiette sonne, tout creux. Une cuillère miniature est encore tiède. Tu sers la soupe ? S'il te plaît, la casserole. Oui. Tiens. Merci. Bravo. Tu as dit les mots. Bonjour, petite casserole. Bonjour. Mila pose l'assiette, tout doux. Une goutte perle au bord de l'assiette. On est encore dans le jardin. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9967,10 +10631,30 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Lina a choisi la dînette. Ça sent le pain chaud. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On montre du doigt, sans courir. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|Mila prend la dînette.
+narrateur|Une petite assiette sonne, tout creux.
+narrateur|Une cuillère miniature est encore tiède.
+papa|Tu sers la soupe ?
+enfant-f|S'il te plaît, la casserole.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci.
+papa|Bravo.
+papa|Tu as dit les mots.
+maman|Bonjour, petite casserole.
+enfant-f|Bonjour.
+narrateur|Mila pose l'assiette, tout doux.
+narrateur|Une goutte perle au bord de l'assiette.
+narrateur|On est encore dans le jardin.
+maman|On dit s'il te plaît.
+maman|On dit merci.</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>assiette</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9995,7 +10679,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On dit encore les mots.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10159,7 +10843,9 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On dit encore les mots.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10187,7 +10873,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint le matin. Le vent est doux. On dit merci. Cette fin-là est celle de le jardin, la dînette et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. La rosée brille encore, tout loin. Ça sent le cacao, un peu. Bonjour, Mila. Bonjour, papa. Mila a encore la dînette, dans le jardin. Une petite assiette a une goutte de rosée. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10327,10 +11013,33 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint le matin. Le vent est doux. On dit merci. Cette fin-là est celle de le jardin, la dînette et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|La rosée brille encore, tout loin.
+narrateur|Ça sent le cacao, un peu.
+papa|Bonjour, Mila.
+enfant-f|Bonjour, papa.
+narrateur|Mila a encore la dînette, dans le jardin.
+narrateur|Une petite assiette a une goutte de rosée.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range la dînette, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10355,7 +11064,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu le matin, dans le jardin. Elle a joué avec la dînette. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10495,7 +11204,15 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu le matin, dans le jardin.
+narrateur|Elle a joué avec la dînette.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10523,7 +11240,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint après la sieste. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Tu es réveillée ? Oui, maman. Mila a encore la dînette, dans le jardin. La dînette est tiède, au soleil. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10663,7 +11380,26 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint après la sieste. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+narrateur|Mila a encore la dînette, dans le jardin.
+narrateur|La dînette est tiède, au soleil.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10691,7 +11427,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu après la sieste, dans le jardin. Elle a joué avec la dînette. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10831,7 +11567,15 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu après la sieste, dans le jardin.
+narrateur|Elle a joué avec la dînette.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10859,7 +11603,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint le soir. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Te voilà, Mila. Bonjour, papa. Mila a encore la dînette, dans le jardin. Loin de la dînette, le banc brille encore. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10999,10 +11743,33 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint le soir. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+papa|Te voilà, Mila.
+enfant-f|Bonjour, papa.
+narrateur|Mila a encore la dînette, dans le jardin.
+narrateur|Loin de la dînette, le banc brille encore.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range la dînette, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11027,7 +11794,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu le soir, dans le jardin. Elle a joué avec la dînette. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11167,7 +11934,15 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu le soir, dans le jardin.
+narrateur|Elle a joué avec la dînette.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11195,7 +11970,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Lina va vers la chambre. Il y a des miettes sur la table. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Lina se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On souffle doucement. Je suis là. On reste ensemble.</t>
+          <t>Mila entre dans la chambre. Le parquet craque, tout petit. Le doudou attend sur l'oreiller. Un rayon pose sur le plaid. Bonjour, doudou. Bonjour, Mila. Tu veux le plaid doux ? Oui. S'il te plaît. Maman pose le plaid sur ses genoux. Le tissu est chaud, un peu lourd. Merci, maman. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le doudou a une oreille froissée.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11335,8 +12110,24 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Lina va vers la chambre. Il y a des miettes sur la table. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Lina se souvient : bonjour, s'il te plaît, merci. Voici le geste : dire le mot. On souffle doucement.
-papa|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Mila entre dans la chambre.
+narrateur|Le parquet craque, tout petit.
+narrateur|Le doudou attend sur l'oreiller.
+narrateur|Un rayon pose sur le plaid.
+enfant-f|Bonjour, doudou.
+maman|Bonjour, Mila.
+maman|Tu veux le plaid doux ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+narrateur|Maman pose le plaid sur ses genoux.
+narrateur|Le tissu est chaud, un peu lourd.
+enfant-f|Merci, maman.
+papa|Bravo.
+papa|Tu as dit les trois mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+narrateur|Le doudou a une oreille froissée.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11364,7 +12155,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Bonjour, s'il te plaît, merci.</t>
+          <t>Maman donne le plaid. Mila dit quoi ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11524,7 +12315,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Bonjour, s'il te plaît, merci.</t>
+          <t>narrateur|Maman donne le plaid.
+papa|Mila dit quoi ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11552,7 +12344,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : dire le mot. Lina respire. Lina retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
+          <t>Oui. On dit merci. On dit bonjour aussi. Mila caresse le plaid, tout doux. Merci, maman. Bravo. Tu as dit merci. Le rayon glisse encore sur l'oreiller.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11696,7 +12488,14 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : dire le mot. Lina respire. Lina retient : bonjour, s'il te plaît, merci. On continue, avec papa.</t>
+          <t>papa|Oui.
+papa|On dit merci.
+papa|On dit bonjour aussi.
+narrateur|Mila caresse le plaid, tout doux.
+enfant-f|Merci, maman.
+maman|Bravo.
+maman|Tu as dit merci.
+narrateur|Le rayon glisse encore sur l'oreiller.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11724,7 +12523,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Trois jeux attendent, tout proches. Les cubes, le livre, ou la dînette ? On demande. On dit merci.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11888,7 +12687,10 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>narrateur|Trois jeux attendent, tout proches.
+maman|Les cubes, le livre, ou la dînette ?
+papa|On demande.
+papa|On dit merci.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11916,7 +12718,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Lina a choisi les cubes. Le vent est doux. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
+          <t>Mila prend les cubes en bois. Un cube rouge sent le pin. Un cube vert fait clic. Tu veux le cube rouge ? S'il te plaît. Papa tend le cube, tout lentement. Merci, papa. Bravo. Tu as demandé. Puis tu as dit merci. On dit s'il te plaît. On dit merci. Mila pose le cube, tout droit. Un cube tapote le parquet, tout doux. On est encore dans la chambre. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12056,10 +12858,30 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Lina a choisi les cubes. Le vent est doux. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On écoute jusqu'au bout. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Mila prend les cubes en bois.
+narrateur|Un cube rouge sent le pin.
+narrateur|Un cube vert fait clic.
+papa|Tu veux le cube rouge ?
+enfant-f|S'il te plaît.
+narrateur|Papa tend le cube, tout lentement.
+enfant-f|Merci, papa.
+maman|Bravo.
+maman|Tu as demandé.
+maman|Puis tu as dit merci.
+papa|On dit s'il te plaît.
+papa|On dit merci.
+narrateur|Mila pose le cube, tout droit.
+narrateur|Un cube tapote le parquet, tout doux.
+narrateur|On est encore dans la chambre.
+maman|On dit s'il te plaît.
+maman|On dit merci.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>cubes</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12084,7 +12906,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On dit encore les mots.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12248,7 +13070,9 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On dit encore les mots.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12276,7 +13100,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint le matin. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. La rosée brille encore, tout loin. Ça sent le cacao, un peu. Bonjour, Mila. Bonjour, papa. Mila a encore les cubes, dans la chambre. Un rayon pose sur la tour de cubes. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12416,10 +13240,33 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint le matin. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|La rosée brille encore, tout loin.
+narrateur|Ça sent le cacao, un peu.
+papa|Bonjour, Mila.
+enfant-f|Bonjour, papa.
+narrateur|Mila a encore les cubes, dans la chambre.
+narrateur|Un rayon pose sur la tour de cubes.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range les cubes, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12444,7 +13291,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu le matin, dans la chambre. Elle a joué avec les cubes. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12584,7 +13431,15 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu le matin, dans la chambre.
+narrateur|Elle a joué avec les cubes.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12612,7 +13467,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint après la sieste. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Tu es réveillée ? Oui, maman. Mila a encore les cubes, dans la chambre. Un cube est contre l'oreiller, tout calme. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12752,7 +13607,26 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint après la sieste. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+narrateur|Mila a encore les cubes, dans la chambre.
+narrateur|Un cube est contre l'oreiller, tout calme.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12780,7 +13654,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu après la sieste, dans la chambre. Elle a joué avec les cubes. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12920,7 +13794,15 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu après la sieste, dans la chambre.
+narrateur|Elle a joué avec les cubes.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12948,7 +13830,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint le soir. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la chambre, les cubes et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Te voilà, Mila. Bonjour, papa. Mila a encore les cubes, dans la chambre. L'ombre des cubes danse sur le mur. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range les cubes, tout doux.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13088,10 +13970,33 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint le soir. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la chambre, les cubes et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+papa|Te voilà, Mila.
+enfant-f|Bonjour, papa.
+narrateur|Mila a encore les cubes, dans la chambre.
+narrateur|L'ombre des cubes danse sur le mur.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range les cubes, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13116,7 +14021,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu le soir, dans la chambre. Elle a joué avec les cubes. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13256,7 +14161,15 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu le soir, dans la chambre.
+narrateur|Elle a joué avec les cubes.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13284,7 +14197,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Lina a choisi le livre. Le sol est un peu froid. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
+          <t>Mila ouvre le livre. La page sent le papier, un peu sec. Une pomme est dessinée, toute rouge. On lit ensemble ? Oui. S'il te plaît. Maman tourne la page, tout doux. Merci, maman. Bravo, Mila. Tu as dit s'il te plaît. Et merci, maintenant. Merci. Mila caresse la pomme du livre. Le rayon colore la page, tout jaune. On est encore dans la chambre. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13424,10 +14337,30 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Lina a choisi le livre. Le sol est un peu froid. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On attend son tour. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Mila ouvre le livre.
+narrateur|La page sent le papier, un peu sec.
+narrateur|Une pomme est dessinée, toute rouge.
+maman|On lit ensemble ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+narrateur|Maman tourne la page, tout doux.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit s'il te plaît.
+maman|Et merci, maintenant.
+enfant-f|Merci.
+narrateur|Mila caresse la pomme du livre.
+narrateur|Le rayon colore la page, tout jaune.
+narrateur|On est encore dans la chambre.
+maman|On dit s'il te plaît.
+maman|On dit merci.</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13452,7 +14385,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On dit encore les mots.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13616,7 +14549,9 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On dit encore les mots.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13644,7 +14579,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint le matin. Le vent est doux. On souffle doucement. Cette fin-là est celle de la chambre, le livre et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. La rosée brille encore, tout loin. Ça sent le cacao, un peu. Bonjour, Mila. Bonjour, papa. Mila a encore le livre, dans la chambre. Le plaid filtre la page, tout jaune. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13784,10 +14719,33 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint le matin. Le vent est doux. On souffle doucement. Cette fin-là est celle de la chambre, le livre et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|La rosée brille encore, tout loin.
+narrateur|Ça sent le cacao, un peu.
+papa|Bonjour, Mila.
+enfant-f|Bonjour, papa.
+narrateur|Mila a encore le livre, dans la chambre.
+narrateur|Le plaid filtre la page, tout jaune.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range le livre, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13812,7 +14770,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu le matin, dans la chambre. Elle a joué avec le livre. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13952,7 +14910,15 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu le matin, dans la chambre.
+narrateur|Elle a joué avec le livre.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -13980,7 +14946,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint après la sieste. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Tu es réveillée ? Oui, maman. Mila a encore le livre, dans la chambre. Le livre est ouvert sur la couverture. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14120,7 +15086,26 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint après la sieste. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+narrateur|Mila a encore le livre, dans la chambre.
+narrateur|Le livre est ouvert sur la couverture.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range le livre, tout doux.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14148,7 +15133,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu après la sieste, dans la chambre. Elle a joué avec le livre. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14288,7 +15273,15 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu après la sieste, dans la chambre.
+narrateur|Elle a joué avec le livre.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14316,7 +15309,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint le soir. Une feuille tombe. On attend son tour. Cette fin-là est celle de la chambre, le livre et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Te voilà, Mila. Bonjour, papa. Mila a encore le livre, dans la chambre. La page sent le doudou, un peu. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range le livre, tout doux.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14456,10 +15449,33 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint le soir. Une feuille tombe. On attend son tour. Cette fin-là est celle de la chambre, le livre et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+papa|Te voilà, Mila.
+enfant-f|Bonjour, papa.
+narrateur|Mila a encore le livre, dans la chambre.
+narrateur|La page sent le doudou, un peu.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range le livre, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14484,7 +15500,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu le soir, dans la chambre. Elle a joué avec le livre. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14624,7 +15640,15 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu le soir, dans la chambre.
+narrateur|Elle a joué avec le livre.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14652,7 +15676,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Lina a choisi la dînette. Une feuille tombe. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On montre du doigt, sans courir. maman n'est pas loin.</t>
+          <t>Mila prend la dînette. Une petite assiette sonne, tout creux. Une cuillère miniature est encore tiède. Tu sers la soupe ? S'il te plaît, la casserole. Oui. Tiens. Merci. Bravo. Tu as dit les mots. Bonjour, petite casserole. Bonjour. Mila pose l'assiette, tout doux. La petite tasse est près du doudou. On est encore dans la chambre. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14792,10 +15816,30 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Lina a choisi la dînette. Une feuille tombe. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : dire le mot. Lina répète tout bas : bonjour, s'il te plaît, merci. On montre du doigt, sans courir. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Mila prend la dînette.
+narrateur|Une petite assiette sonne, tout creux.
+narrateur|Une cuillère miniature est encore tiède.
+papa|Tu sers la soupe ?
+enfant-f|S'il te plaît, la casserole.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci.
+papa|Bravo.
+papa|Tu as dit les mots.
+maman|Bonjour, petite casserole.
+enfant-f|Bonjour.
+narrateur|Mila pose l'assiette, tout doux.
+narrateur|La petite tasse est près du doudou.
+narrateur|On est encore dans la chambre.
+maman|On dit s'il te plaît.
+maman|On dit merci.</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>assiette</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14820,7 +15864,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>Quel moment, maintenant ? Le matin, après la sieste, ou le soir ? On dit encore les mots.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -14984,7 +16028,9 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|Quel moment, maintenant ?
+papa|Le matin, après la sieste, ou le soir ?
+maman|On dit encore les mots.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15012,7 +16058,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint le matin. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Le matin, la lumière est claire. La rosée brille encore, tout loin. Ça sent le cacao, un peu. Bonjour, Mila. Bonjour, papa. Mila a encore la dînette, dans la chambre. Une tasse miniature est près du lit. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15152,10 +16198,33 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint le matin. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et le matin. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|Le matin, la lumière est claire.
+narrateur|La rosée brille encore, tout loin.
+narrateur|Ça sent le cacao, un peu.
+papa|Bonjour, Mila.
+enfant-f|Bonjour, papa.
+narrateur|Mila a encore la dînette, dans la chambre.
+narrateur|Une tasse miniature est près du lit.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range la dînette, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15180,7 +16249,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu le matin, dans la chambre. Elle a joué avec la dînette. Un oiseau picore encore, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15320,7 +16389,15 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu le matin, dans la chambre.
+narrateur|Elle a joué avec la dînette.
+narrateur|Un oiseau picore encore, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15348,7 +16425,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint après la sieste. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les joues sont chaudes. La couverture a un pli, tout doux. La maison est calme, encore un peu. Tu es réveillée ? Oui, maman. Mila a encore la dînette, dans la chambre. La dînette attend au pied du lit. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15488,7 +16565,26 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint après la sieste. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et après la sieste. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les joues sont chaudes.
+narrateur|La couverture a un pli, tout doux.
+narrateur|La maison est calme, encore un peu.
+maman|Tu es réveillée ?
+enfant-f|Oui, maman.
+narrateur|Mila a encore la dînette, dans la chambre.
+narrateur|La dînette attend au pied du lit.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15516,7 +16612,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu après la sieste, dans la chambre. Elle a joué avec la dînette. La couverture redescend, tout calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15656,7 +16752,15 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu après la sieste, dans la chambre.
+narrateur|Elle a joué avec la dînette.
+narrateur|La couverture redescend, tout calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15684,7 +16788,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Lina rejoint le soir. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la chambre, la dînette et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
+          <t>Le soir, la lampe fait un rond. Ça sent le pain, tout chaud. Les chaussons font toc, sur le bois. Te voilà, Mila. Bonjour, papa. Mila a encore la dînette, dans la chambre. Une petite assiette reflète la veilleuse. Tu veux encore jouer ? Oui. S'il te plaît. Oui. Tiens. Merci, maman. Bravo, Mila. Tu as dit les mots. Bonjour. S'il te plaît. Merci. Merci, papa. Mila range la dînette, tout doux.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15824,10 +16928,33 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Lina rejoint le soir. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la chambre, la dînette et le soir. Lina a appris : Bonjour, s'il te plaît, merci. Voici le geste : dire le mot. Lina a entendu : bonjour, s'il te plaît, merci. Lina dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|Le soir, la lampe fait un rond.
+narrateur|Ça sent le pain, tout chaud.
+narrateur|Les chaussons font toc, sur le bois.
+papa|Te voilà, Mila.
+enfant-f|Bonjour, papa.
+narrateur|Mila a encore la dînette, dans la chambre.
+narrateur|Une petite assiette reflète la veilleuse.
+papa|Tu veux encore jouer ?
+enfant-f|Oui.
+enfant-f|S'il te plaît.
+maman|Oui.
+maman|Tiens.
+enfant-f|Merci, maman.
+papa|Bravo, Mila.
+papa|Tu as dit les mots.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+enfant-f|Merci, papa.
+narrateur|Mila range la dînette, tout doux.</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15852,7 +16979,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Bonjour. S'il te plaît. Merci. Bravo, Mila. Tu as fait du bon travail. Mila a vécu le soir, dans la chambre. Elle a joué avec la dînette. La lampe reste allumée, tout doux. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -15992,7 +17119,15 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|Bonjour.
+enfant-f|S'il te plaît.
+enfant-f|Merci.
+maman|Bravo, Mila.
+papa|Tu as fait du bon travail.
+narrateur|Mila a vécu le soir, dans la chambre.
+narrateur|Elle a joué avec la dînette.
+narrateur|La lampe reste allumée, tout doux.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16014,7 +17149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16052,6 +17187,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>
